--- a/LISTAS/mi/SOPORTE U LIDIMA.xlsx
+++ b/LISTAS/mi/SOPORTE U LIDIMA.xlsx
@@ -794,14 +794,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45189.54995376568</v>
+        <v>45217</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -847,20 +843,6 @@
       </c>
       <c r="E11" s="7" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26" ht="18" customHeight="1" s="1">
       <c r="A26" s="21" t="inlineStr">
         <is>
@@ -893,7 +875,7 @@
       </c>
       <c r="C27" s="29" t="n"/>
       <c r="D27" s="30" t="n">
-        <v>94.3</v>
+        <v>103.73</v>
       </c>
       <c r="E27" s="27" t="n"/>
       <c r="F27" s="27" t="n"/>
@@ -912,7 +894,7 @@
       </c>
       <c r="C28" s="26" t="n"/>
       <c r="D28" s="30" t="n">
-        <v>94.3</v>
+        <v>103.73</v>
       </c>
       <c r="E28" s="27" t="n"/>
       <c r="F28" s="27" t="n"/>
@@ -931,7 +913,7 @@
       </c>
       <c r="C29" s="26" t="n"/>
       <c r="D29" s="30" t="n">
-        <v>94.3</v>
+        <v>103.73</v>
       </c>
       <c r="E29" s="27" t="n"/>
       <c r="F29" s="27" t="n"/>
@@ -947,7 +929,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
@@ -957,15 +938,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE U LIDIMA.xlsx
+++ b/LISTAS/mi/SOPORTE U LIDIMA.xlsx
@@ -794,7 +794,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45217</v>
+        <v>45230</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="C27" s="29" t="n"/>
       <c r="D27" s="30" t="n">
-        <v>103.73</v>
+        <v>94.3</v>
       </c>
       <c r="E27" s="27" t="n"/>
       <c r="F27" s="27" t="n"/>
@@ -894,7 +894,7 @@
       </c>
       <c r="C28" s="26" t="n"/>
       <c r="D28" s="30" t="n">
-        <v>103.73</v>
+        <v>94.3</v>
       </c>
       <c r="E28" s="27" t="n"/>
       <c r="F28" s="27" t="n"/>
@@ -913,7 +913,7 @@
       </c>
       <c r="C29" s="26" t="n"/>
       <c r="D29" s="30" t="n">
-        <v>103.73</v>
+        <v>94.3</v>
       </c>
       <c r="E29" s="27" t="n"/>
       <c r="F29" s="27" t="n"/>

--- a/LISTAS/mi/SOPORTE U LIDIMA.xlsx
+++ b/LISTAS/mi/SOPORTE U LIDIMA.xlsx
@@ -794,7 +794,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45230</v>
+        <v>45231</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/SOPORTE U LIDIMA.xlsx
+++ b/LISTAS/mi/SOPORTE U LIDIMA.xlsx
@@ -794,7 +794,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45231</v>
+        <v>45232</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/SOPORTE U LIDIMA.xlsx
+++ b/LISTAS/mi/SOPORTE U LIDIMA.xlsx
@@ -794,7 +794,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45232</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/SOPORTE U LIDIMA.xlsx
+++ b/LISTAS/mi/SOPORTE U LIDIMA.xlsx
@@ -938,15 +938,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B26:C26"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE U LIDIMA.xlsx
+++ b/LISTAS/mi/SOPORTE U LIDIMA.xlsx
@@ -794,7 +794,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -938,15 +938,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE U LIDIMA.xlsx
+++ b/LISTAS/mi/SOPORTE U LIDIMA.xlsx
@@ -938,15 +938,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B26:C26"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE U LIDIMA.xlsx
+++ b/LISTAS/mi/SOPORTE U LIDIMA.xlsx
@@ -794,7 +794,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45254</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -938,15 +938,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE U LIDIMA.xlsx
+++ b/LISTAS/mi/SOPORTE U LIDIMA.xlsx
@@ -794,7 +794,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/SOPORTE U LIDIMA.xlsx
+++ b/LISTAS/mi/SOPORTE U LIDIMA.xlsx
@@ -794,10 +794,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45266</v>
+        <v>45230.54209965279</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -843,6 +847,20 @@
       </c>
       <c r="E11" s="7" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26" ht="18" customHeight="1" s="1">
       <c r="A26" s="21" t="inlineStr">
         <is>
@@ -875,7 +893,7 @@
       </c>
       <c r="C27" s="29" t="n"/>
       <c r="D27" s="30" t="n">
-        <v>94.3</v>
+        <v>108.44</v>
       </c>
       <c r="E27" s="27" t="n"/>
       <c r="F27" s="27" t="n"/>
@@ -894,7 +912,7 @@
       </c>
       <c r="C28" s="26" t="n"/>
       <c r="D28" s="30" t="n">
-        <v>94.3</v>
+        <v>108.44</v>
       </c>
       <c r="E28" s="27" t="n"/>
       <c r="F28" s="27" t="n"/>
@@ -913,7 +931,7 @@
       </c>
       <c r="C29" s="26" t="n"/>
       <c r="D29" s="30" t="n">
-        <v>94.3</v>
+        <v>108.44</v>
       </c>
       <c r="E29" s="27" t="n"/>
       <c r="F29" s="27" t="n"/>
@@ -929,6 +947,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
@@ -938,15 +957,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE U LIDIMA.xlsx
+++ b/LISTAS/mi/SOPORTE U LIDIMA.xlsx
@@ -794,14 +794,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45230.54209965279</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -847,20 +843,6 @@
       </c>
       <c r="E11" s="7" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26" ht="18" customHeight="1" s="1">
       <c r="A26" s="21" t="inlineStr">
         <is>
@@ -893,7 +875,7 @@
       </c>
       <c r="C27" s="29" t="n"/>
       <c r="D27" s="30" t="n">
-        <v>108.44</v>
+        <v>94.3</v>
       </c>
       <c r="E27" s="27" t="n"/>
       <c r="F27" s="27" t="n"/>
@@ -912,7 +894,7 @@
       </c>
       <c r="C28" s="26" t="n"/>
       <c r="D28" s="30" t="n">
-        <v>108.44</v>
+        <v>94.3</v>
       </c>
       <c r="E28" s="27" t="n"/>
       <c r="F28" s="27" t="n"/>
@@ -931,7 +913,7 @@
       </c>
       <c r="C29" s="26" t="n"/>
       <c r="D29" s="30" t="n">
-        <v>108.44</v>
+        <v>94.3</v>
       </c>
       <c r="E29" s="27" t="n"/>
       <c r="F29" s="27" t="n"/>
@@ -947,7 +929,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
@@ -957,15 +938,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
